--- a/artfynd/A 7608-2023 artfynd.xlsx
+++ b/artfynd/A 7608-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7608-2023 artfynd.xlsx
+++ b/artfynd/A 7608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>102190535</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622250.0704993034</v>
+        <v>622251</v>
       </c>
       <c r="R2" t="n">
-        <v>6861609.170335921</v>
+        <v>6861609</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -802,50 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105316182</v>
+        <v>105315324</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>myran, Hls</t>
+          <t>Ishockey-, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622291.9516954849</v>
+        <v>622197</v>
       </c>
       <c r="R3" t="n">
-        <v>6861284.810810058</v>
+        <v>6861674</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,21 +865,11 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,11 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Spår på tallåga. Relativt färsk.</t>
-        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -924,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105315326</v>
+        <v>105315325</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ishockey-, Hls</t>
+          <t>bana, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622213.025536171</v>
+        <v>622182</v>
       </c>
       <c r="R4" t="n">
-        <v>6861613.511390363</v>
+        <v>6861540</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,21 +967,11 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,11 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>På gammal tall strax intill stigen. Två fruktkroppar.</t>
-        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1046,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105315325</v>
+        <v>105315326</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,14 +1032,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>bana, Hls</t>
+          <t>Ishockey-, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622182.0709064172</v>
+        <v>622213</v>
       </c>
       <c r="R5" t="n">
-        <v>6861540.15111239</v>
+        <v>6861614</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,21 +1069,11 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1142,6 +1082,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På gammal tall strax intill stigen. Två fruktkroppar.</t>
+        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -1163,50 +1108,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105316181</v>
+        <v>107139102</v>
       </c>
       <c r="B6" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>myran, Hls</t>
+          <t>Strömsbruk, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622195.2980067962</v>
+        <v>622343</v>
       </c>
       <c r="R6" t="n">
-        <v>6861368.722694199</v>
+        <v>6861240</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,22 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,81 +1198,103 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På torrträd av tall. Relativt färsk.</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105316179</v>
+        <v>83912554</v>
       </c>
       <c r="B7" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>102987</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herrgårds-, Hls</t>
+          <t>strömsbruk, Strömsbruk, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622037.0679701761</v>
+        <v>622102</v>
       </c>
       <c r="R7" t="n">
-        <v>6861309.699070029</v>
+        <v>6861656</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,22 +1318,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,41 +1344,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Färska spår på död tall med barken delvis kvar.</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105316180</v>
+        <v>105316179</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,14 +1391,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>myran, Hls</t>
+          <t>Herrgårds-, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622112.8173876058</v>
+        <v>622037</v>
       </c>
       <c r="R8" t="n">
-        <v>6861307.683477341</v>
+        <v>6861310</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1480,21 +1428,11 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1503,6 +1441,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Färska spår på död tall med barken delvis kvar.</t>
+        </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -1524,50 +1467,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105315324</v>
+        <v>105316180</v>
       </c>
       <c r="B9" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ishockey-, Hls</t>
+          <t>myran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622197.1340543486</v>
+        <v>622113</v>
       </c>
       <c r="R9" t="n">
-        <v>6861674.332844336</v>
+        <v>6861308</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1597,19 +1535,9 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,61 +1569,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107139102</v>
+        <v>105316181</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömsbruk, Hls</t>
+          <t>myran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622343.713762062</v>
+        <v>622195</v>
       </c>
       <c r="R10" t="n">
-        <v>6861239.435850253</v>
+        <v>6861369</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1722,22 +1634,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,42 +1648,138 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>På torrträd av tall. Relativt färsk.</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105316182</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>myran, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622292</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6861285</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Harmånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Spår på tallåga. Relativt färsk.</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7608-2023 artfynd.xlsx
+++ b/artfynd/A 7608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102190535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315326</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107139102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83912554</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316181</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,8 +1830,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>